--- a/output/pdf_financials_xlsx/LABZ.xlsx
+++ b/output/pdf_financials_xlsx/LABZ.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.730336</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.531519</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.683655</v>
       </c>
     </row>
     <row r="93">
@@ -3005,7 +3005,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3034,7 +3038,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3690,7 +3698,11 @@
           <t>Reserve 12</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>3.720574</v>
       </c>
@@ -3719,7 +3731,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.009762</v>
       </c>

--- a/output/pdf_financials_xlsx/LABZ.xlsx
+++ b/output/pdf_financials_xlsx/LABZ.xlsx
@@ -583,7 +583,7 @@
         <v>1.344054</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.278973</v>
+        <v>0.922864</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>0.49991</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.278773</v>
+        <v>-0.922664</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.024516</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001236</v>
       </c>
     </row>
     <row r="13">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-12.545912</v>
+        <v>-12.570428</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.014345</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.909652</v>
+        <v>-0.910888</v>
       </c>
     </row>
     <row r="28">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-12.143018</v>
+        <v>-12.167534</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.097846</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.909652</v>
+        <v>-0.910888</v>
       </c>
     </row>
     <row r="30">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1854.017591994589</v>
+        <v>-1857.760738491229</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>4.455823158749914</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-36386.08</v>
+        <v>-36435.52</v>
       </c>
     </row>
     <row r="31">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.112895</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.112895</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -5861,7 +5861,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>-0.112895</v>
       </c>
@@ -6648,7 +6652,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -6861,7 +6865,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7076,7 +7080,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8353,7 +8357,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">

--- a/output/pdf_financials_xlsx/LABZ.xlsx
+++ b/output/pdf_financials_xlsx/LABZ.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.274826</v>
+        <v>0.572398</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.438671</v>
+        <v>0.51334</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.234832</v>
+        <v>0.291019</v>
       </c>
     </row>
     <row r="8">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-12.545912</v>
+        <v>-12.384207</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.014345</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.161705</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.5410740000000001</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.556414</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.274511</v>
       </c>
     </row>
     <row r="65">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.595936</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.659691</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.217611</v>
       </c>
     </row>
     <row r="68">
@@ -4613,7 +4613,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -5958,7 +5962,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -6714,7 +6722,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>0.297572</v>
       </c>
@@ -8543,7 +8555,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="n">
         <v>-12.384207</v>
       </c>
@@ -8572,7 +8588,11 @@
           <t>Loss from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E189" s="5" t="n">
         <v>-0.161705</v>
       </c>
